--- a/onlineCompcorImplementation/results/kscDataset.xlsx
+++ b/onlineCompcorImplementation/results/kscDataset.xlsx
@@ -465,26 +465,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004628373512604453</v>
+        <v>0.0004485485052972149</v>
       </c>
       <c r="C2" t="n">
-        <v>0.007063927076476877</v>
+        <v>0.0006902053500439712</v>
       </c>
       <c r="D2" t="n">
-        <v>2.926928276378492</v>
+        <v>1.661596458996915</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.7616672756134618</v>
+        <v>-0.642014969911249</v>
       </c>
       <c r="F2" t="n">
-        <v>0.555297739168735</v>
+        <v>0.7438444390218831</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.6938125368976892</v>
+        <v>-0.5939900191673316</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>atis</t>
+          <t>yahoo</t>
         </is>
       </c>
     </row>
@@ -495,26 +495,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8673149068908403</v>
+        <v>0.8400954628347037</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8146813634056198</v>
+        <v>0.7828874585701948</v>
       </c>
       <c r="D3" t="n">
-        <v>3.294584729568711</v>
+        <v>3.243238825940776</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8395503599434631</v>
+        <v>0.8166355376094886</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6761102686425552</v>
+        <v>0.6557559613404993</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8471408190804047</v>
+        <v>0.8290022052596624</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>atis</t>
+          <t>yahoo</t>
         </is>
       </c>
     </row>
@@ -525,26 +525,26 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.840625211804276</v>
+        <v>0.7831635722061957</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7835740414517963</v>
+        <v>0.7192065599494133</v>
       </c>
       <c r="D4" t="n">
-        <v>0.287122849460255</v>
+        <v>0.2872390104705866</v>
       </c>
       <c r="E4" t="n">
-        <v>0.808979271940848</v>
+        <v>0.7767173662016713</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8216789314207557</v>
+        <v>0.7975633858849891</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8553804170676202</v>
+        <v>0.8142907220616352</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>atis</t>
+          <t>yahoo</t>
         </is>
       </c>
     </row>
@@ -555,26 +555,26 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9699565695332257</v>
+        <v>0.9058922361024625</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9534202241113556</v>
+        <v>0.8657561414290262</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05263437194907728</v>
+        <v>0.05222193957313534</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8836098026415389</v>
+        <v>0.7535989207102292</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8345011942666797</v>
+        <v>0.5910575547777963</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9142074364851891</v>
+        <v>0.8063790555219892</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>atis</t>
+          <t>yahoo</t>
         </is>
       </c>
     </row>
@@ -585,26 +585,26 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7322468700623128</v>
+        <v>0.6959669950691965</v>
       </c>
       <c r="C6" t="n">
-        <v>0.685909681097842</v>
+        <v>0.650900082103218</v>
       </c>
       <c r="D6" t="n">
-        <v>24.41325610069451</v>
+        <v>24.37814207199321</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5389255832291338</v>
+        <v>0.4351645614970001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4122632707082046</v>
+        <v>0.1312114110395641</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6119346105459497</v>
+        <v>0.4944629141980008</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>atis</t>
+          <t>yahoo</t>
         </is>
       </c>
     </row>
@@ -615,26 +615,26 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9762927473979844</v>
+        <v>0.9398781913609272</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9608619334754677</v>
+        <v>0.9101392672113074</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03556766962600393</v>
+        <v>0.03407086031729885</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9483747034642857</v>
+        <v>0.9268373662217309</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9000068029127353</v>
+        <v>0.8845253639241949</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9474360064452421</v>
+        <v>0.9350981831185909</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>atis</t>
+          <t>yahoo</t>
         </is>
       </c>
     </row>
@@ -645,26 +645,26 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6444295740192403</v>
+        <v>0.7071445553592837</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6063130805570139</v>
+        <v>0.6534169266809351</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2871140543164838</v>
+        <v>0.2873837117408962</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4592010785762258</v>
+        <v>0.5132982915151214</v>
       </c>
       <c r="F8" t="n">
-        <v>0.570950999294171</v>
+        <v>0.4994058181270692</v>
       </c>
       <c r="G8" t="n">
-        <v>0.684593251990491</v>
+        <v>0.6361236491444587</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>atis</t>
+          <t>yahoo</t>
         </is>
       </c>
     </row>
@@ -675,26 +675,26 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9409751521813723</v>
+        <v>0.9120829309052091</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9090676022839055</v>
+        <v>0.8794503747567282</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01002434286800214</v>
+        <v>0.007192729707836839</v>
       </c>
       <c r="E9" t="n">
-        <v>0.913275927802503</v>
+        <v>0.8744098381334028</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8452757928901606</v>
+        <v>0.7896698580286738</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9313931332491696</v>
+        <v>0.8985323651490581</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>atis</t>
+          <t>yahoo</t>
         </is>
       </c>
     </row>
@@ -705,26 +705,26 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.953805209432068</v>
+        <v>0.9260517935586083</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9273573217540559</v>
+        <v>0.8920880004795555</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001413396295181412</v>
+        <v>0.0009719997376528575</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9442371538995793</v>
+        <v>0.9040421605144178</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9134751570893376</v>
+        <v>0.8419200850521342</v>
       </c>
       <c r="G10" t="n">
-        <v>0.960233545449913</v>
+        <v>0.9252426176756972</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>atis</t>
+          <t>yahoo</t>
         </is>
       </c>
     </row>
@@ -735,26 +735,26 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7553362763537471</v>
+        <v>0.6963421533928926</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7173088631497999</v>
+        <v>0.6663861390100834</v>
       </c>
       <c r="D11" t="n">
-        <v>4.825748408229051</v>
+        <v>3.054573883893243</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4975964519837529</v>
+        <v>0.380048477561065</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1011437228168462</v>
+        <v>0.08803888595352771</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4772118401106415</v>
+        <v>0.3850311947635027</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>atis</t>
+          <t>yahoo</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
         <v>0.003219094049570657</v>
       </c>
       <c r="C12" t="n">
-        <v>0.00506020494150483</v>
+        <v>0.005060204941504829</v>
       </c>
       <c r="D12" t="n">
         <v>2.630551574346676</v>
@@ -777,7 +777,7 @@
         <v>-0.7031315311422478</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7499992380431573</v>
+        <v>0.7499992380431574</v>
       </c>
       <c r="G12" t="n">
         <v>-0.6399755733868648</v>
@@ -1065,26 +1065,26 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.004836524164749815</v>
+        <v>0.01090756278937757</v>
       </c>
       <c r="C22" t="n">
-        <v>0.006591333158095374</v>
+        <v>0.01596351353540692</v>
       </c>
       <c r="D22" t="n">
-        <v>2.979242214134129</v>
+        <v>1.308672391472623</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6842544320651499</v>
+        <v>-0.8412676329959127</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4756880809457311</v>
+        <v>0.6856299964485919</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6362778884283865</v>
+        <v>-0.7193731354585539</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>clinc150</t>
+          <t>medicalAbstracts</t>
         </is>
       </c>
     </row>
@@ -1095,26 +1095,26 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8433124256037481</v>
+        <v>0.8631338772467139</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7837059707434088</v>
+        <v>0.806593075607674</v>
       </c>
       <c r="D23" t="n">
-        <v>3.265137915562551</v>
+        <v>3.251676180008122</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8239215155523312</v>
+        <v>0.8381945049001823</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6584617431192656</v>
+        <v>0.6902315331011625</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8360492276245119</v>
+        <v>0.8539120306591983</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>clinc150</t>
+          <t>medicalAbstracts</t>
         </is>
       </c>
     </row>
@@ -1125,26 +1125,26 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.821781753167533</v>
+        <v>0.8648006709959462</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7630394163935741</v>
+        <v>0.8127613032646716</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2869887584292357</v>
+        <v>0.2870369371841692</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8006010659473121</v>
+        <v>0.8371639929498401</v>
       </c>
       <c r="F24" t="n">
-        <v>0.795258078318504</v>
+        <v>0.8353675101431594</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8419424648612853</v>
+        <v>0.87121821152833</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>clinc150</t>
+          <t>medicalAbstracts</t>
         </is>
       </c>
     </row>
@@ -1155,26 +1155,26 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9226766659465322</v>
+        <v>0.9609717262472095</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8856281668795289</v>
+        <v>0.9387983219728672</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0516841972721229</v>
+        <v>0.05226756696255956</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8313525067649054</v>
+        <v>0.8884301187013387</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7466015710291527</v>
+        <v>0.849438278189513</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8753143363004794</v>
+        <v>0.9209390062245597</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>clinc150</t>
+          <t>medicalAbstracts</t>
         </is>
       </c>
     </row>
@@ -1185,26 +1185,26 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7576281442344758</v>
+        <v>0.7702502758750693</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7078543556417596</v>
+        <v>0.7237701108646499</v>
       </c>
       <c r="D26" t="n">
-        <v>23.93349696505232</v>
+        <v>24.11956312425493</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5715612958662989</v>
+        <v>0.5665013493450028</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3555167811515059</v>
+        <v>0.3983870927302092</v>
       </c>
       <c r="G26" t="n">
-        <v>0.6376081732841167</v>
+        <v>0.6504200802189938</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>clinc150</t>
+          <t>medicalAbstracts</t>
         </is>
       </c>
     </row>
@@ -1215,26 +1215,26 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.9465282366870422</v>
+        <v>0.9698805450359432</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9182809940159317</v>
+        <v>0.950265359138879</v>
       </c>
       <c r="D27" t="n">
-        <v>0.03425253305988275</v>
+        <v>0.03453255850542689</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9319564889187737</v>
+        <v>0.9479557659905192</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8905831110088871</v>
+        <v>0.9043242820669378</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9390000178106229</v>
+        <v>0.9484048133571286</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>clinc150</t>
+          <t>medicalAbstracts</t>
         </is>
       </c>
     </row>
@@ -1245,26 +1245,26 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6946627175759424</v>
+        <v>0.6738203163720469</v>
       </c>
       <c r="C28" t="n">
-        <v>0.6508132414382563</v>
+        <v>0.6282009895728281</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2870419451035457</v>
+        <v>0.2871529728012324</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5314025513417524</v>
+        <v>0.5261187846871598</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5793573674816561</v>
+        <v>0.6123884628836301</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6884325539566568</v>
+        <v>0.7052610748294992</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>clinc150</t>
+          <t>medicalAbstracts</t>
         </is>
       </c>
     </row>
@@ -1275,26 +1275,26 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8830911748571381</v>
+        <v>0.9710840698827028</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8430451670017035</v>
+        <v>0.9524148191998488</v>
       </c>
       <c r="D29" t="n">
-        <v>0.01023721448718906</v>
+        <v>0.003299148429901796</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8494355458367107</v>
+        <v>0.9483429923535114</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7554429441938224</v>
+        <v>0.9093383396905774</v>
       </c>
       <c r="G29" t="n">
-        <v>0.8792161505545508</v>
+        <v>0.9610126288678729</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>clinc150</t>
+          <t>medicalAbstracts</t>
         </is>
       </c>
     </row>
@@ -1305,26 +1305,26 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9291432358186447</v>
+        <v>0.9861667450342487</v>
       </c>
       <c r="C30" t="n">
-        <v>0.898086978898946</v>
+        <v>0.9775031739889464</v>
       </c>
       <c r="D30" t="n">
-        <v>0.001445946748505084</v>
+        <v>0.00038164860159913</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9060918546293328</v>
+        <v>0.9633562749882331</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8467595604092781</v>
+        <v>0.9381875636425725</v>
       </c>
       <c r="G30" t="n">
-        <v>0.9275725227641941</v>
+        <v>0.9738642640712781</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>clinc150</t>
+          <t>medicalAbstracts</t>
         </is>
       </c>
     </row>
@@ -1335,26 +1335,26 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6852375067247858</v>
+        <v>0.7866978707316143</v>
       </c>
       <c r="C31" t="n">
-        <v>0.6631349330586045</v>
+        <v>0.7501168453399644</v>
       </c>
       <c r="D31" t="n">
-        <v>5.073211952801968</v>
+        <v>2.779082188224955</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3795114395397973</v>
+        <v>0.5263866462407911</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1136691386755202</v>
+        <v>0.1339311469491252</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3812597848112482</v>
+        <v>0.5011200708296347</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>clinc150</t>
+          <t>medicalAbstracts</t>
         </is>
       </c>
     </row>
@@ -1365,26 +1365,26 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.001918920264162274</v>
+        <v>0.000510911626783905</v>
       </c>
       <c r="C32" t="n">
-        <v>0.002813713193736339</v>
+        <v>0.0007674151435407888</v>
       </c>
       <c r="D32" t="n">
-        <v>1.697110667347108</v>
+        <v>1.739070543753545</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.6911932046571697</v>
+        <v>-0.6334190813790164</v>
       </c>
       <c r="F32" t="n">
-        <v>0.7154707400492315</v>
+        <v>0.7194461035330484</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.5946046262215997</v>
+        <v>-0.5754620053859386</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>clinicalDialogueSummarizations</t>
+          <t>huffPostNews</t>
         </is>
       </c>
     </row>
@@ -1395,26 +1395,26 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8564660271236556</v>
+        <v>0.8472360733393486</v>
       </c>
       <c r="C33" t="n">
-        <v>0.8007455756422125</v>
+        <v>0.7918123186237996</v>
       </c>
       <c r="D33" t="n">
-        <v>3.23718218670483</v>
+        <v>3.245204383605337</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8312087746961847</v>
+        <v>0.8183563945375818</v>
       </c>
       <c r="F33" t="n">
-        <v>0.6895674066474277</v>
+        <v>0.6565647997062768</v>
       </c>
       <c r="G33" t="n">
-        <v>0.851259704268065</v>
+        <v>0.8298114172948318</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>clinicalDialogueSummarizations</t>
+          <t>huffPostNews</t>
         </is>
       </c>
     </row>
@@ -1425,26 +1425,26 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8436303835351828</v>
+        <v>0.8341577682395253</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7891644570180133</v>
+        <v>0.7810563999484462</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2871544846757471</v>
+        <v>0.2870649737180718</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8191042005528227</v>
+        <v>0.8159562715435495</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8255954619951607</v>
+        <v>0.8205889520195301</v>
       </c>
       <c r="G34" t="n">
-        <v>0.8581433816642359</v>
+        <v>0.8540314719189834</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>clinicalDialogueSummarizations</t>
+          <t>huffPostNews</t>
         </is>
       </c>
     </row>
@@ -1455,26 +1455,26 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9409133450461098</v>
+        <v>0.9206516582156761</v>
       </c>
       <c r="C35" t="n">
-        <v>0.9095999943310771</v>
+        <v>0.8841575951475218</v>
       </c>
       <c r="D35" t="n">
-        <v>0.05150189863228229</v>
+        <v>0.05115114032622915</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8736005385861194</v>
+        <v>0.8028154172167625</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8167089788316576</v>
+        <v>0.6896597743488754</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9038956209483952</v>
+        <v>0.8523527801312333</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>clinicalDialogueSummarizations</t>
+          <t>huffPostNews</t>
         </is>
       </c>
     </row>
@@ -1485,26 +1485,26 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7634045895868546</v>
+        <v>0.697113994649824</v>
       </c>
       <c r="C36" t="n">
-        <v>0.7135012623741813</v>
+        <v>0.6523123716158973</v>
       </c>
       <c r="D36" t="n">
-        <v>24.1763479125518</v>
+        <v>24.10981279308245</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5972248004625548</v>
+        <v>0.4484383050473901</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4152327432363832</v>
+        <v>0.1733452861463986</v>
       </c>
       <c r="G36" t="n">
-        <v>0.6587798330222342</v>
+        <v>0.5191609583539829</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>clinicalDialogueSummarizations</t>
+          <t>huffPostNews</t>
         </is>
       </c>
     </row>
@@ -1515,26 +1515,26 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.9569339954334999</v>
+        <v>0.9423249411184114</v>
       </c>
       <c r="C37" t="n">
-        <v>0.9302837085818565</v>
+        <v>0.9128573373212012</v>
       </c>
       <c r="D37" t="n">
-        <v>0.03463679605450325</v>
+        <v>0.03425807052289872</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9420801221964186</v>
+        <v>0.9297104542867484</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9046841054606497</v>
+        <v>0.8864725214209433</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9487462052208243</v>
+        <v>0.9380029281961865</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>clinicalDialogueSummarizations</t>
+          <t>huffPostNews</t>
         </is>
       </c>
     </row>
@@ -1545,26 +1545,26 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6861990981373932</v>
+        <v>0.6962801476911216</v>
       </c>
       <c r="C38" t="n">
-        <v>0.6364709200082654</v>
+        <v>0.6470939312548848</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2871950781970121</v>
+        <v>0.2871181197571722</v>
       </c>
       <c r="E38" t="n">
-        <v>0.537848509016055</v>
+        <v>0.5337400412710231</v>
       </c>
       <c r="F38" t="n">
-        <v>0.598115345852355</v>
+        <v>0.557617320238401</v>
       </c>
       <c r="G38" t="n">
-        <v>0.6969726112339263</v>
+        <v>0.6674628173216789</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>clinicalDialogueSummarizations</t>
+          <t>huffPostNews</t>
         </is>
       </c>
     </row>
@@ -1575,26 +1575,26 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.9092633526710637</v>
+        <v>0.8857738083891438</v>
       </c>
       <c r="C39" t="n">
-        <v>0.8670338434000129</v>
+        <v>0.8422608951640784</v>
       </c>
       <c r="D39" t="n">
-        <v>0.007268918032714755</v>
+        <v>0.008617820510998844</v>
       </c>
       <c r="E39" t="n">
-        <v>0.8930099524471645</v>
+        <v>0.8489739874719812</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8251642052012972</v>
+        <v>0.7513234750693797</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9182872943655237</v>
+        <v>0.8806762047841479</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>clinicalDialogueSummarizations</t>
+          <t>huffPostNews</t>
         </is>
       </c>
     </row>
@@ -1605,26 +1605,26 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.9366619037180123</v>
+        <v>0.9318155571299673</v>
       </c>
       <c r="C40" t="n">
-        <v>0.9033989949458909</v>
+        <v>0.9003793149398966</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0007130254680178263</v>
+        <v>0.001206491415589297</v>
       </c>
       <c r="E40" t="n">
-        <v>0.91923968882712</v>
+        <v>0.9117080181576893</v>
       </c>
       <c r="F40" t="n">
-        <v>0.8680779472591615</v>
+        <v>0.8559757188995923</v>
       </c>
       <c r="G40" t="n">
-        <v>0.9394274416536573</v>
+        <v>0.9310571895046221</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>clinicalDialogueSummarizations</t>
+          <t>huffPostNews</t>
         </is>
       </c>
     </row>
@@ -1635,26 +1635,26 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6840967553702975</v>
+        <v>0.7634885170311818</v>
       </c>
       <c r="C41" t="n">
-        <v>0.6560152674118868</v>
+        <v>0.724977115377748</v>
       </c>
       <c r="D41" t="n">
-        <v>3.070693689818212</v>
+        <v>3.132653746859419</v>
       </c>
       <c r="E41" t="n">
-        <v>0.3684040627127699</v>
+        <v>0.5362982133439369</v>
       </c>
       <c r="F41" t="n">
-        <v>0.05827055890907257</v>
+        <v>0.2451307683496861</v>
       </c>
       <c r="G41" t="n">
-        <v>0.3704744151256827</v>
+        <v>0.5566564252456236</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>clinicalDialogueSummarizations</t>
+          <t>huffPostNews</t>
         </is>
       </c>
     </row>
@@ -1665,26 +1665,26 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.000510911626783905</v>
+        <v>0.004836524164749815</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0007674151435407888</v>
+        <v>0.006591333158095373</v>
       </c>
       <c r="D42" t="n">
-        <v>1.739070543753545</v>
+        <v>2.979242214134129</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.6334190813790164</v>
+        <v>-0.6842544320651499</v>
       </c>
       <c r="F42" t="n">
-        <v>0.7194461035330484</v>
+        <v>0.4756880809457311</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.5754620053859386</v>
+        <v>-0.6362778884283865</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>huffPostNews</t>
+          <t>clinc150</t>
         </is>
       </c>
     </row>
@@ -1695,26 +1695,26 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8472360733393486</v>
+        <v>0.8433124256037481</v>
       </c>
       <c r="C43" t="n">
-        <v>0.7918123186237996</v>
+        <v>0.7837059707434088</v>
       </c>
       <c r="D43" t="n">
-        <v>3.245204383605337</v>
+        <v>3.265137915562551</v>
       </c>
       <c r="E43" t="n">
-        <v>0.8183563945375818</v>
+        <v>0.8239215155523312</v>
       </c>
       <c r="F43" t="n">
-        <v>0.6565647997062768</v>
+        <v>0.6584617431192656</v>
       </c>
       <c r="G43" t="n">
-        <v>0.8298114172948318</v>
+        <v>0.8360492276245119</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>huffPostNews</t>
+          <t>clinc150</t>
         </is>
       </c>
     </row>
@@ -1725,26 +1725,26 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8341577682395253</v>
+        <v>0.821781753167533</v>
       </c>
       <c r="C44" t="n">
-        <v>0.7810563999484462</v>
+        <v>0.7630394163935741</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2870649737180718</v>
+        <v>0.2869887584292357</v>
       </c>
       <c r="E44" t="n">
-        <v>0.8159562715435495</v>
+        <v>0.8006010659473121</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8205889520195301</v>
+        <v>0.795258078318504</v>
       </c>
       <c r="G44" t="n">
-        <v>0.8540314719189834</v>
+        <v>0.8419424648612853</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>huffPostNews</t>
+          <t>clinc150</t>
         </is>
       </c>
     </row>
@@ -1755,26 +1755,26 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.9206516582156761</v>
+        <v>0.9226766659465322</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8841575951475218</v>
+        <v>0.8856281668795289</v>
       </c>
       <c r="D45" t="n">
-        <v>0.05115114032622915</v>
+        <v>0.0516841972721229</v>
       </c>
       <c r="E45" t="n">
-        <v>0.8028154172167625</v>
+        <v>0.8313525067649054</v>
       </c>
       <c r="F45" t="n">
-        <v>0.6896597743488754</v>
+        <v>0.7466015710291527</v>
       </c>
       <c r="G45" t="n">
-        <v>0.8523527801312333</v>
+        <v>0.8753143363004794</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>huffPostNews</t>
+          <t>clinc150</t>
         </is>
       </c>
     </row>
@@ -1785,26 +1785,26 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.697113994649824</v>
+        <v>0.7576281442344758</v>
       </c>
       <c r="C46" t="n">
-        <v>0.6523123716158973</v>
+        <v>0.7078543556417596</v>
       </c>
       <c r="D46" t="n">
-        <v>24.10981279308245</v>
+        <v>23.93349696505232</v>
       </c>
       <c r="E46" t="n">
-        <v>0.4484383050473901</v>
+        <v>0.5715612958662989</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1733452861463986</v>
+        <v>0.3555167811515059</v>
       </c>
       <c r="G46" t="n">
-        <v>0.5191609583539829</v>
+        <v>0.6376081732841167</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>huffPostNews</t>
+          <t>clinc150</t>
         </is>
       </c>
     </row>
@@ -1815,26 +1815,26 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.9423249411184114</v>
+        <v>0.9465282366870422</v>
       </c>
       <c r="C47" t="n">
-        <v>0.9128573373212012</v>
+        <v>0.9182809940159317</v>
       </c>
       <c r="D47" t="n">
-        <v>0.03425807052289872</v>
+        <v>0.03425253305988275</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9297104542867484</v>
+        <v>0.9319564889187737</v>
       </c>
       <c r="F47" t="n">
-        <v>0.8864725214209433</v>
+        <v>0.8905831110088871</v>
       </c>
       <c r="G47" t="n">
-        <v>0.9380029281961865</v>
+        <v>0.9390000178106229</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>huffPostNews</t>
+          <t>clinc150</t>
         </is>
       </c>
     </row>
@@ -1845,26 +1845,26 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6962801476911216</v>
+        <v>0.6946627175759424</v>
       </c>
       <c r="C48" t="n">
-        <v>0.6470939312548848</v>
+        <v>0.6508132414382563</v>
       </c>
       <c r="D48" t="n">
-        <v>0.2871181197571722</v>
+        <v>0.2870419451035457</v>
       </c>
       <c r="E48" t="n">
-        <v>0.5337400412710231</v>
+        <v>0.5314025513417524</v>
       </c>
       <c r="F48" t="n">
-        <v>0.557617320238401</v>
+        <v>0.5793573674816561</v>
       </c>
       <c r="G48" t="n">
-        <v>0.6674628173216789</v>
+        <v>0.6884325539566568</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>huffPostNews</t>
+          <t>clinc150</t>
         </is>
       </c>
     </row>
@@ -1875,26 +1875,26 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8857738083891438</v>
+        <v>0.8830911748571381</v>
       </c>
       <c r="C49" t="n">
-        <v>0.8422608951640784</v>
+        <v>0.8430451670017035</v>
       </c>
       <c r="D49" t="n">
-        <v>0.008617820510998844</v>
+        <v>0.01023721448718906</v>
       </c>
       <c r="E49" t="n">
-        <v>0.8489739874719812</v>
+        <v>0.8494355458367107</v>
       </c>
       <c r="F49" t="n">
-        <v>0.7513234750693797</v>
+        <v>0.7554429441938224</v>
       </c>
       <c r="G49" t="n">
-        <v>0.8806762047841479</v>
+        <v>0.8792161505545508</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>huffPostNews</t>
+          <t>clinc150</t>
         </is>
       </c>
     </row>
@@ -1905,26 +1905,26 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.9318155571299673</v>
+        <v>0.9291432358186448</v>
       </c>
       <c r="C50" t="n">
-        <v>0.9003793149398966</v>
+        <v>0.898086978898946</v>
       </c>
       <c r="D50" t="n">
-        <v>0.001206491415589297</v>
+        <v>0.001445946748505084</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9117080181576893</v>
+        <v>0.9060918546293328</v>
       </c>
       <c r="F50" t="n">
-        <v>0.8559757188995923</v>
+        <v>0.8467595604092781</v>
       </c>
       <c r="G50" t="n">
-        <v>0.9310571895046221</v>
+        <v>0.9275725227641941</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>huffPostNews</t>
+          <t>clinc150</t>
         </is>
       </c>
     </row>
@@ -1935,26 +1935,26 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7634885170311818</v>
+        <v>0.6852375067247858</v>
       </c>
       <c r="C51" t="n">
-        <v>0.724977115377748</v>
+        <v>0.6631349330586045</v>
       </c>
       <c r="D51" t="n">
-        <v>3.132653746859419</v>
+        <v>5.073211952801968</v>
       </c>
       <c r="E51" t="n">
-        <v>0.5362982133439369</v>
+        <v>0.3795114395397973</v>
       </c>
       <c r="F51" t="n">
-        <v>0.2451307683496861</v>
+        <v>0.1136691386755202</v>
       </c>
       <c r="G51" t="n">
-        <v>0.5566564252456236</v>
+        <v>0.3812597848112482</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>huffPostNews</t>
+          <t>clinc150</t>
         </is>
       </c>
     </row>
@@ -1965,26 +1965,26 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.01090756278937757</v>
+        <v>0.000410542875539565</v>
       </c>
       <c r="C52" t="n">
-        <v>0.01596351353540692</v>
+        <v>0.0005566063250923363</v>
       </c>
       <c r="D52" t="n">
-        <v>1.308672391472623</v>
+        <v>1.831872634775853</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.8412676329959127</v>
+        <v>-0.7365713194861188</v>
       </c>
       <c r="F52" t="n">
-        <v>0.6856299964485919</v>
+        <v>0.7238804993575308</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.7193731354585539</v>
+        <v>-0.653370835851668</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>medicalAbstracts</t>
+          <t>syntheticCareHomeNurseNotes</t>
         </is>
       </c>
     </row>
@@ -1995,26 +1995,26 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8631338772467139</v>
+        <v>0.8646883485408804</v>
       </c>
       <c r="C53" t="n">
-        <v>0.806593075607674</v>
+        <v>0.810857278935105</v>
       </c>
       <c r="D53" t="n">
-        <v>3.251676180008122</v>
+        <v>3.263048483093971</v>
       </c>
       <c r="E53" t="n">
-        <v>0.8381945049001823</v>
+        <v>0.8417393726999934</v>
       </c>
       <c r="F53" t="n">
-        <v>0.6902315331011625</v>
+        <v>0.6902574072028079</v>
       </c>
       <c r="G53" t="n">
-        <v>0.8539120306591983</v>
+        <v>0.8536888864071673</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>medicalAbstracts</t>
+          <t>syntheticCareHomeNurseNotes</t>
         </is>
       </c>
     </row>
@@ -2025,26 +2025,26 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8648006709959462</v>
+        <v>0.8715904012420203</v>
       </c>
       <c r="C54" t="n">
-        <v>0.8127613032646716</v>
+        <v>0.8239649774715494</v>
       </c>
       <c r="D54" t="n">
-        <v>0.2870369371841692</v>
+        <v>0.2871841822362564</v>
       </c>
       <c r="E54" t="n">
-        <v>0.8371639929498401</v>
+        <v>0.8549336680548212</v>
       </c>
       <c r="F54" t="n">
-        <v>0.8353675101431594</v>
+        <v>0.8608951932167295</v>
       </c>
       <c r="G54" t="n">
-        <v>0.87121821152833</v>
+        <v>0.8876345739865824</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>medicalAbstracts</t>
+          <t>syntheticCareHomeNurseNotes</t>
         </is>
       </c>
     </row>
@@ -2055,26 +2055,26 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.9609717262472095</v>
+        <v>0.9614082548598492</v>
       </c>
       <c r="C55" t="n">
-        <v>0.9387983219728672</v>
+        <v>0.9406053669333374</v>
       </c>
       <c r="D55" t="n">
-        <v>0.05226756696255956</v>
+        <v>0.05142023982257489</v>
       </c>
       <c r="E55" t="n">
-        <v>0.8884301187013387</v>
+        <v>0.8790002044264178</v>
       </c>
       <c r="F55" t="n">
-        <v>0.849438278189513</v>
+        <v>0.8231620817635898</v>
       </c>
       <c r="G55" t="n">
-        <v>0.9209390062245597</v>
+        <v>0.9079587868855417</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>medicalAbstracts</t>
+          <t>syntheticCareHomeNurseNotes</t>
         </is>
       </c>
     </row>
@@ -2085,26 +2085,26 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7702502758750693</v>
+        <v>0.7633323775665384</v>
       </c>
       <c r="C56" t="n">
-        <v>0.7237701108646499</v>
+        <v>0.7146872360111088</v>
       </c>
       <c r="D56" t="n">
-        <v>24.11956312425493</v>
+        <v>24.39360401629475</v>
       </c>
       <c r="E56" t="n">
-        <v>0.5665013493450028</v>
+        <v>0.5882538942477183</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3983870927302092</v>
+        <v>0.4365422280943194</v>
       </c>
       <c r="G56" t="n">
-        <v>0.6504200802189938</v>
+        <v>0.6634492961853622</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>medicalAbstracts</t>
+          <t>syntheticCareHomeNurseNotes</t>
         </is>
       </c>
     </row>
@@ -2115,26 +2115,26 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.9698805450359432</v>
+        <v>0.9719873621683675</v>
       </c>
       <c r="C57" t="n">
-        <v>0.950265359138879</v>
+        <v>0.9532793853030888</v>
       </c>
       <c r="D57" t="n">
-        <v>0.03453255850542689</v>
+        <v>0.03482039571692556</v>
       </c>
       <c r="E57" t="n">
-        <v>0.9479557659905192</v>
+        <v>0.9426063278721716</v>
       </c>
       <c r="F57" t="n">
-        <v>0.9043242820669378</v>
+        <v>0.8916366412527704</v>
       </c>
       <c r="G57" t="n">
-        <v>0.9484048133571286</v>
+        <v>0.9442703108721481</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>medicalAbstracts</t>
+          <t>syntheticCareHomeNurseNotes</t>
         </is>
       </c>
     </row>
@@ -2145,26 +2145,26 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6738203163720469</v>
+        <v>0.6820739583465711</v>
       </c>
       <c r="C58" t="n">
-        <v>0.6282009895728281</v>
+        <v>0.6340456305144876</v>
       </c>
       <c r="D58" t="n">
-        <v>0.2871529728012324</v>
+        <v>0.2871312046450465</v>
       </c>
       <c r="E58" t="n">
-        <v>0.5261187846871598</v>
+        <v>0.5369976376806442</v>
       </c>
       <c r="F58" t="n">
-        <v>0.6123884628836301</v>
+        <v>0.6094019823557798</v>
       </c>
       <c r="G58" t="n">
-        <v>0.7052610748294992</v>
+        <v>0.7020357450465736</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>medicalAbstracts</t>
+          <t>syntheticCareHomeNurseNotes</t>
         </is>
       </c>
     </row>
@@ -2175,26 +2175,26 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.9710840698827028</v>
+        <v>0.9567353892115374</v>
       </c>
       <c r="C59" t="n">
-        <v>0.9524148191998488</v>
+        <v>0.9317643449229486</v>
       </c>
       <c r="D59" t="n">
-        <v>0.003299148429901796</v>
+        <v>0.00864149313436195</v>
       </c>
       <c r="E59" t="n">
-        <v>0.9483429923535114</v>
+        <v>0.9361805102404505</v>
       </c>
       <c r="F59" t="n">
-        <v>0.9093383396905774</v>
+        <v>0.893906496792258</v>
       </c>
       <c r="G59" t="n">
-        <v>0.9610126288678729</v>
+        <v>0.9526560707432273</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>medicalAbstracts</t>
+          <t>syntheticCareHomeNurseNotes</t>
         </is>
       </c>
     </row>
@@ -2205,26 +2205,26 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.9861667450342487</v>
+        <v>0.9432637768091262</v>
       </c>
       <c r="C60" t="n">
-        <v>0.9775031739889464</v>
+        <v>0.9143734546929007</v>
       </c>
       <c r="D60" t="n">
-        <v>0.00038164860159913</v>
+        <v>0.001166531802884021</v>
       </c>
       <c r="E60" t="n">
-        <v>0.9633562749882331</v>
+        <v>0.9218485790675477</v>
       </c>
       <c r="F60" t="n">
-        <v>0.9381875636425725</v>
+        <v>0.8654927928915094</v>
       </c>
       <c r="G60" t="n">
-        <v>0.9738642640712781</v>
+        <v>0.9384531122835033</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>medicalAbstracts</t>
+          <t>syntheticCareHomeNurseNotes</t>
         </is>
       </c>
     </row>
@@ -2235,26 +2235,26 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7866978707316143</v>
+        <v>0.695673460818327</v>
       </c>
       <c r="C61" t="n">
-        <v>0.7501168453399644</v>
+        <v>0.6667705806147853</v>
       </c>
       <c r="D61" t="n">
-        <v>2.779082188224955</v>
+        <v>3.107932065644191</v>
       </c>
       <c r="E61" t="n">
-        <v>0.5263866462407911</v>
+        <v>0.3794336907242288</v>
       </c>
       <c r="F61" t="n">
-        <v>0.1339311469491252</v>
+        <v>0.03788480553749762</v>
       </c>
       <c r="G61" t="n">
-        <v>0.5011200708296347</v>
+        <v>0.3832947372623888</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>medicalAbstracts</t>
+          <t>syntheticCareHomeNurseNotes</t>
         </is>
       </c>
     </row>
@@ -2265,26 +2265,26 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.000235420452668095</v>
+        <v>0.001918920264162274</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0004127482308203938</v>
+        <v>0.002813713193736339</v>
       </c>
       <c r="D62" t="n">
-        <v>1.672112088627344</v>
+        <v>1.697110667347108</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.8221137989795443</v>
+        <v>-0.6911932046571697</v>
       </c>
       <c r="F62" t="n">
-        <v>0.62700918120305</v>
+        <v>0.7154707400492315</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.7467932878021347</v>
+        <v>-0.5946046262215997</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>simSUM</t>
+          <t>clinicalDialogueSummarizations</t>
         </is>
       </c>
     </row>
@@ -2295,26 +2295,26 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8731111824185507</v>
+        <v>0.8564660271236556</v>
       </c>
       <c r="C63" t="n">
-        <v>0.8180986687801225</v>
+        <v>0.8007455756422125</v>
       </c>
       <c r="D63" t="n">
-        <v>3.347524238499106</v>
+        <v>3.23718218670483</v>
       </c>
       <c r="E63" t="n">
-        <v>0.8400375494672571</v>
+        <v>0.8312087746961847</v>
       </c>
       <c r="F63" t="n">
-        <v>0.6565656400397997</v>
+        <v>0.6895674066474277</v>
       </c>
       <c r="G63" t="n">
-        <v>0.8389894580909901</v>
+        <v>0.851259704268065</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>simSUM</t>
+          <t>clinicalDialogueSummarizations</t>
         </is>
       </c>
     </row>
@@ -2325,26 +2325,26 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.8726672538940217</v>
+        <v>0.8436303835351828</v>
       </c>
       <c r="C64" t="n">
-        <v>0.8230574331488478</v>
+        <v>0.7891644570180133</v>
       </c>
       <c r="D64" t="n">
-        <v>0.2871103977557009</v>
+        <v>0.2871544846757471</v>
       </c>
       <c r="E64" t="n">
-        <v>0.8469063803745827</v>
+        <v>0.8191042005528227</v>
       </c>
       <c r="F64" t="n">
-        <v>0.8454574195777885</v>
+        <v>0.8255954619951607</v>
       </c>
       <c r="G64" t="n">
-        <v>0.8819948884524398</v>
+        <v>0.8581433816642359</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>simSUM</t>
+          <t>clinicalDialogueSummarizations</t>
         </is>
       </c>
     </row>
@@ -2355,26 +2355,26 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.977777521847611</v>
+        <v>0.9409133450461098</v>
       </c>
       <c r="C65" t="n">
-        <v>0.9641989219753105</v>
+        <v>0.9095999943310771</v>
       </c>
       <c r="D65" t="n">
-        <v>0.0529987326076698</v>
+        <v>0.05150189863228229</v>
       </c>
       <c r="E65" t="n">
-        <v>0.8717502926704139</v>
+        <v>0.8736005385861194</v>
       </c>
       <c r="F65" t="n">
-        <v>0.82128241671931</v>
+        <v>0.8167089788316576</v>
       </c>
       <c r="G65" t="n">
-        <v>0.9112991103017286</v>
+        <v>0.9038956209483952</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>simSUM</t>
+          <t>clinicalDialogueSummarizations</t>
         </is>
       </c>
     </row>
@@ -2385,26 +2385,26 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.6668444234052198</v>
+        <v>0.7634045895868546</v>
       </c>
       <c r="C66" t="n">
-        <v>0.6304030619511596</v>
+        <v>0.7135012623741813</v>
       </c>
       <c r="D66" t="n">
-        <v>24.16326388116144</v>
+        <v>24.1763479125518</v>
       </c>
       <c r="E66" t="n">
-        <v>0.3896966034378708</v>
+        <v>0.5972248004625548</v>
       </c>
       <c r="F66" t="n">
-        <v>0.205591673384034</v>
+        <v>0.4152327432363832</v>
       </c>
       <c r="G66" t="n">
-        <v>0.4781950319965991</v>
+        <v>0.6587798330222342</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>simSUM</t>
+          <t>clinicalDialogueSummarizations</t>
         </is>
       </c>
     </row>
@@ -2415,26 +2415,26 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.9779931121249476</v>
+        <v>0.9569339954334998</v>
       </c>
       <c r="C67" t="n">
-        <v>0.9623835545862623</v>
+        <v>0.9302837085818565</v>
       </c>
       <c r="D67" t="n">
-        <v>0.03595371445723732</v>
+        <v>0.03463679605450325</v>
       </c>
       <c r="E67" t="n">
-        <v>0.9452655552654462</v>
+        <v>0.9420801221964186</v>
       </c>
       <c r="F67" t="n">
-        <v>0.8900262163790617</v>
+        <v>0.9046841054606497</v>
       </c>
       <c r="G67" t="n">
-        <v>0.94178515962577</v>
+        <v>0.9487462052208243</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>simSUM</t>
+          <t>clinicalDialogueSummarizations</t>
         </is>
       </c>
     </row>
@@ -2445,26 +2445,26 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.6261786113688063</v>
+        <v>0.6861990981373932</v>
       </c>
       <c r="C68" t="n">
-        <v>0.5874383626363301</v>
+        <v>0.6364709200082654</v>
       </c>
       <c r="D68" t="n">
-        <v>0.2871637556896399</v>
+        <v>0.2871950781970121</v>
       </c>
       <c r="E68" t="n">
-        <v>0.405550087388465</v>
+        <v>0.537848509016055</v>
       </c>
       <c r="F68" t="n">
-        <v>0.5398600278634579</v>
+        <v>0.598115345852355</v>
       </c>
       <c r="G68" t="n">
-        <v>0.6481815388581066</v>
+        <v>0.6969726112339263</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>simSUM</t>
+          <t>clinicalDialogueSummarizations</t>
         </is>
       </c>
     </row>
@@ -2475,26 +2475,26 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.9556300488844269</v>
+        <v>0.9092633526710637</v>
       </c>
       <c r="C69" t="n">
-        <v>0.9308547436728589</v>
+        <v>0.8670338434000129</v>
       </c>
       <c r="D69" t="n">
-        <v>0.005082026618111147</v>
+        <v>0.007268918032714755</v>
       </c>
       <c r="E69" t="n">
-        <v>0.9238655611814102</v>
+        <v>0.8930099524471645</v>
       </c>
       <c r="F69" t="n">
-        <v>0.8636202963817813</v>
+        <v>0.8251642052012972</v>
       </c>
       <c r="G69" t="n">
-        <v>0.9405870605548037</v>
+        <v>0.9182872943655237</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>simSUM</t>
+          <t>clinicalDialogueSummarizations</t>
         </is>
       </c>
     </row>
@@ -2505,26 +2505,26 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.9793836204340294</v>
+        <v>0.9366619037180123</v>
       </c>
       <c r="C70" t="n">
-        <v>0.9665647879849443</v>
+        <v>0.9033989949458909</v>
       </c>
       <c r="D70" t="n">
-        <v>0.0007287940325423212</v>
+        <v>0.0007130254680178263</v>
       </c>
       <c r="E70" t="n">
-        <v>0.9576472388286423</v>
+        <v>0.91923968882712</v>
       </c>
       <c r="F70" t="n">
-        <v>0.9273108837056866</v>
+        <v>0.8680779472591615</v>
       </c>
       <c r="G70" t="n">
-        <v>0.9683126202900519</v>
+        <v>0.9394274416536573</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>simSUM</t>
+          <t>clinicalDialogueSummarizations</t>
         </is>
       </c>
     </row>
@@ -2535,26 +2535,26 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.8783389355564311</v>
+        <v>0.6840967553702975</v>
       </c>
       <c r="C71" t="n">
-        <v>0.8621255921001751</v>
+        <v>0.6560152674118868</v>
       </c>
       <c r="D71" t="n">
-        <v>2.994085204413774</v>
+        <v>3.070693689818212</v>
       </c>
       <c r="E71" t="n">
-        <v>0.6308458301664055</v>
+        <v>0.3684040627127699</v>
       </c>
       <c r="F71" t="n">
-        <v>0.2567999697140133</v>
+        <v>0.05827055890907257</v>
       </c>
       <c r="G71" t="n">
-        <v>0.5730571227741328</v>
+        <v>0.3704744151256827</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>simSUM</t>
+          <t>clinicalDialogueSummarizations</t>
         </is>
       </c>
     </row>
@@ -2565,26 +2565,26 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.000410542875539565</v>
+        <v>0.000235420452668095</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0005566063250923363</v>
+        <v>0.0004127482308203938</v>
       </c>
       <c r="D72" t="n">
-        <v>1.831872634775853</v>
+        <v>1.672112088627344</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.7365713194861188</v>
+        <v>-0.8221137989795443</v>
       </c>
       <c r="F72" t="n">
-        <v>0.7238804993575308</v>
+        <v>0.62700918120305</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.653370835851668</v>
+        <v>-0.7467932878021347</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>syntheticCareHomeNurseNotes</t>
+          <t>simSUM</t>
         </is>
       </c>
     </row>
@@ -2595,26 +2595,26 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.8646883485408804</v>
+        <v>0.8731111824185507</v>
       </c>
       <c r="C73" t="n">
-        <v>0.810857278935105</v>
+        <v>0.8180986687801225</v>
       </c>
       <c r="D73" t="n">
-        <v>3.263048483093971</v>
+        <v>3.347524238499106</v>
       </c>
       <c r="E73" t="n">
-        <v>0.8417393726999934</v>
+        <v>0.8400375494672571</v>
       </c>
       <c r="F73" t="n">
-        <v>0.6902574072028079</v>
+        <v>0.6565656400397997</v>
       </c>
       <c r="G73" t="n">
-        <v>0.8536888864071673</v>
+        <v>0.8389894580909901</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>syntheticCareHomeNurseNotes</t>
+          <t>simSUM</t>
         </is>
       </c>
     </row>
@@ -2625,26 +2625,26 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.8715904012420203</v>
+        <v>0.8726672538940217</v>
       </c>
       <c r="C74" t="n">
-        <v>0.8239649774715494</v>
+        <v>0.8230574331488478</v>
       </c>
       <c r="D74" t="n">
-        <v>0.2871841822362564</v>
+        <v>0.2871103977557009</v>
       </c>
       <c r="E74" t="n">
-        <v>0.8549336680548212</v>
+        <v>0.8469063803745827</v>
       </c>
       <c r="F74" t="n">
-        <v>0.8608951932167295</v>
+        <v>0.8454574195777885</v>
       </c>
       <c r="G74" t="n">
-        <v>0.8876345739865824</v>
+        <v>0.8819948884524398</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>syntheticCareHomeNurseNotes</t>
+          <t>simSUM</t>
         </is>
       </c>
     </row>
@@ -2655,26 +2655,26 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.9614082548598492</v>
+        <v>0.977777521847611</v>
       </c>
       <c r="C75" t="n">
-        <v>0.9406053669333374</v>
+        <v>0.9641989219753105</v>
       </c>
       <c r="D75" t="n">
-        <v>0.05142023982257489</v>
+        <v>0.0529987326076698</v>
       </c>
       <c r="E75" t="n">
-        <v>0.8790002044264178</v>
+        <v>0.8717502926704139</v>
       </c>
       <c r="F75" t="n">
-        <v>0.8231620817635898</v>
+        <v>0.82128241671931</v>
       </c>
       <c r="G75" t="n">
-        <v>0.9079587868855417</v>
+        <v>0.9112991103017286</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>syntheticCareHomeNurseNotes</t>
+          <t>simSUM</t>
         </is>
       </c>
     </row>
@@ -2685,26 +2685,26 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7633323775665384</v>
+        <v>0.6668444234052198</v>
       </c>
       <c r="C76" t="n">
-        <v>0.7146872360111088</v>
+        <v>0.6304030619511596</v>
       </c>
       <c r="D76" t="n">
-        <v>24.39360401629475</v>
+        <v>24.16326388116144</v>
       </c>
       <c r="E76" t="n">
-        <v>0.5882538942477183</v>
+        <v>0.3896966034378708</v>
       </c>
       <c r="F76" t="n">
-        <v>0.4365422280943194</v>
+        <v>0.205591673384034</v>
       </c>
       <c r="G76" t="n">
-        <v>0.6634492961853622</v>
+        <v>0.4781950319965991</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>syntheticCareHomeNurseNotes</t>
+          <t>simSUM</t>
         </is>
       </c>
     </row>
@@ -2715,26 +2715,26 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.9719873621683675</v>
+        <v>0.9779931121249476</v>
       </c>
       <c r="C77" t="n">
-        <v>0.9532793853030888</v>
+        <v>0.9623835545862623</v>
       </c>
       <c r="D77" t="n">
-        <v>0.03482039571692556</v>
+        <v>0.03595371445723732</v>
       </c>
       <c r="E77" t="n">
-        <v>0.9426063278721716</v>
+        <v>0.9452655552654462</v>
       </c>
       <c r="F77" t="n">
-        <v>0.8916366412527704</v>
+        <v>0.8900262163790617</v>
       </c>
       <c r="G77" t="n">
-        <v>0.9442703108721481</v>
+        <v>0.94178515962577</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>syntheticCareHomeNurseNotes</t>
+          <t>simSUM</t>
         </is>
       </c>
     </row>
@@ -2745,26 +2745,26 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6820739583465711</v>
+        <v>0.6261786113688064</v>
       </c>
       <c r="C78" t="n">
-        <v>0.6340456305144876</v>
+        <v>0.5874383626363301</v>
       </c>
       <c r="D78" t="n">
-        <v>0.2871312046450465</v>
+        <v>0.2871637556896399</v>
       </c>
       <c r="E78" t="n">
-        <v>0.5369976376806442</v>
+        <v>0.405550087388465</v>
       </c>
       <c r="F78" t="n">
-        <v>0.6094019823557798</v>
+        <v>0.5398600278634578</v>
       </c>
       <c r="G78" t="n">
-        <v>0.7020357450465736</v>
+        <v>0.6481815388581066</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>syntheticCareHomeNurseNotes</t>
+          <t>simSUM</t>
         </is>
       </c>
     </row>
@@ -2775,26 +2775,26 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.9567353892115374</v>
+        <v>0.9556300488844269</v>
       </c>
       <c r="C79" t="n">
-        <v>0.9317643449229486</v>
+        <v>0.9308547436728589</v>
       </c>
       <c r="D79" t="n">
-        <v>0.008641493134361952</v>
+        <v>0.005082026618111147</v>
       </c>
       <c r="E79" t="n">
-        <v>0.9361805102404505</v>
+        <v>0.9238655611814102</v>
       </c>
       <c r="F79" t="n">
-        <v>0.893906496792258</v>
+        <v>0.8636202963817813</v>
       </c>
       <c r="G79" t="n">
-        <v>0.9526560707432273</v>
+        <v>0.9405870605548037</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>syntheticCareHomeNurseNotes</t>
+          <t>simSUM</t>
         </is>
       </c>
     </row>
@@ -2805,26 +2805,26 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.9432637768091262</v>
+        <v>0.9793836204340294</v>
       </c>
       <c r="C80" t="n">
-        <v>0.9143734546929007</v>
+        <v>0.9665647879849443</v>
       </c>
       <c r="D80" t="n">
-        <v>0.001166531802884021</v>
+        <v>0.0007287940325423212</v>
       </c>
       <c r="E80" t="n">
-        <v>0.9218485790675477</v>
+        <v>0.9576472388286423</v>
       </c>
       <c r="F80" t="n">
-        <v>0.8654927928915094</v>
+        <v>0.9273108837056866</v>
       </c>
       <c r="G80" t="n">
-        <v>0.9384531122835033</v>
+        <v>0.9683126202900519</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>syntheticCareHomeNurseNotes</t>
+          <t>simSUM</t>
         </is>
       </c>
     </row>
@@ -2835,26 +2835,26 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.695673460818327</v>
+        <v>0.8783389355564311</v>
       </c>
       <c r="C81" t="n">
-        <v>0.6667705806147853</v>
+        <v>0.8621255921001751</v>
       </c>
       <c r="D81" t="n">
-        <v>3.107932065644191</v>
+        <v>2.994085204413774</v>
       </c>
       <c r="E81" t="n">
-        <v>0.3794336907242288</v>
+        <v>0.6308458301664055</v>
       </c>
       <c r="F81" t="n">
-        <v>0.03788480553749762</v>
+        <v>0.2567999697140133</v>
       </c>
       <c r="G81" t="n">
-        <v>0.3832947372623888</v>
+        <v>0.5730571227741328</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>syntheticCareHomeNurseNotes</t>
+          <t>simSUM</t>
         </is>
       </c>
     </row>
@@ -2865,26 +2865,26 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.0004485485052972149</v>
+        <v>0.004628373512604453</v>
       </c>
       <c r="C82" t="n">
-        <v>0.0006902053500439712</v>
+        <v>0.007063927076476877</v>
       </c>
       <c r="D82" t="n">
-        <v>1.661596458996915</v>
+        <v>2.926928276378492</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.642014969911249</v>
+        <v>-0.7616672756134618</v>
       </c>
       <c r="F82" t="n">
-        <v>0.743844439021883</v>
+        <v>0.555297739168735</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.5939900191673316</v>
+        <v>-0.6938125368976892</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>atis</t>
         </is>
       </c>
     </row>
@@ -2895,26 +2895,26 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.8400954628347037</v>
+        <v>0.8673149068908403</v>
       </c>
       <c r="C83" t="n">
-        <v>0.7828874585701948</v>
+        <v>0.8146813634056198</v>
       </c>
       <c r="D83" t="n">
-        <v>3.243238825940776</v>
+        <v>3.294584729568711</v>
       </c>
       <c r="E83" t="n">
-        <v>0.8166355376094886</v>
+        <v>0.8395503599434631</v>
       </c>
       <c r="F83" t="n">
-        <v>0.6557559613404993</v>
+        <v>0.6761102686425552</v>
       </c>
       <c r="G83" t="n">
-        <v>0.8290022052596624</v>
+        <v>0.8471408190804047</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>atis</t>
         </is>
       </c>
     </row>
@@ -2925,26 +2925,26 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7831635722061957</v>
+        <v>0.840625211804276</v>
       </c>
       <c r="C84" t="n">
-        <v>0.7192065599494133</v>
+        <v>0.7835740414517963</v>
       </c>
       <c r="D84" t="n">
-        <v>0.2872390104705866</v>
+        <v>0.287122849460255</v>
       </c>
       <c r="E84" t="n">
-        <v>0.7767173662016713</v>
+        <v>0.808979271940848</v>
       </c>
       <c r="F84" t="n">
-        <v>0.7975633858849891</v>
+        <v>0.8216789314207557</v>
       </c>
       <c r="G84" t="n">
-        <v>0.8142907220616352</v>
+        <v>0.8553804170676202</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>atis</t>
         </is>
       </c>
     </row>
@@ -2955,26 +2955,26 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.9058922361024625</v>
+        <v>0.9699565695332257</v>
       </c>
       <c r="C85" t="n">
-        <v>0.8657561414290262</v>
+        <v>0.9534202241113556</v>
       </c>
       <c r="D85" t="n">
-        <v>0.05222193957313534</v>
+        <v>0.05263437194907728</v>
       </c>
       <c r="E85" t="n">
-        <v>0.7535989207102292</v>
+        <v>0.8836098026415389</v>
       </c>
       <c r="F85" t="n">
-        <v>0.5910575547777963</v>
+        <v>0.8345011942666797</v>
       </c>
       <c r="G85" t="n">
-        <v>0.8063790555219892</v>
+        <v>0.9142074364851891</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>atis</t>
         </is>
       </c>
     </row>
@@ -2985,26 +2985,26 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.6959669950691965</v>
+        <v>0.7322468700623128</v>
       </c>
       <c r="C86" t="n">
-        <v>0.650900082103218</v>
+        <v>0.685909681097842</v>
       </c>
       <c r="D86" t="n">
-        <v>24.37814207199321</v>
+        <v>24.41325610069451</v>
       </c>
       <c r="E86" t="n">
-        <v>0.4351645614970001</v>
+        <v>0.5389255832291338</v>
       </c>
       <c r="F86" t="n">
-        <v>0.1312114110395641</v>
+        <v>0.4122632707082046</v>
       </c>
       <c r="G86" t="n">
-        <v>0.4944629141980008</v>
+        <v>0.6119346105459497</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>atis</t>
         </is>
       </c>
     </row>
@@ -3015,26 +3015,26 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.9398781913609272</v>
+        <v>0.9762927473979844</v>
       </c>
       <c r="C87" t="n">
-        <v>0.9101392672113074</v>
+        <v>0.9608619334754677</v>
       </c>
       <c r="D87" t="n">
-        <v>0.03407086031729885</v>
+        <v>0.03556766962600393</v>
       </c>
       <c r="E87" t="n">
-        <v>0.9268373662217309</v>
+        <v>0.9483747034642857</v>
       </c>
       <c r="F87" t="n">
-        <v>0.8845253639241949</v>
+        <v>0.9000068029127353</v>
       </c>
       <c r="G87" t="n">
-        <v>0.9350981831185909</v>
+        <v>0.9474360064452421</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>atis</t>
         </is>
       </c>
     </row>
@@ -3045,26 +3045,26 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.7071445553592837</v>
+        <v>0.6444295740192403</v>
       </c>
       <c r="C88" t="n">
-        <v>0.6534169266809351</v>
+        <v>0.6063130805570139</v>
       </c>
       <c r="D88" t="n">
-        <v>0.2873837117408962</v>
+        <v>0.2871140543164838</v>
       </c>
       <c r="E88" t="n">
-        <v>0.5132982915151214</v>
+        <v>0.4592010785762258</v>
       </c>
       <c r="F88" t="n">
-        <v>0.4994058181270692</v>
+        <v>0.570950999294171</v>
       </c>
       <c r="G88" t="n">
-        <v>0.6361236491444587</v>
+        <v>0.684593251990491</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>atis</t>
         </is>
       </c>
     </row>
@@ -3075,26 +3075,26 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.9120829309052091</v>
+        <v>0.9409751521813723</v>
       </c>
       <c r="C89" t="n">
-        <v>0.8794503747567282</v>
+        <v>0.9090676022839055</v>
       </c>
       <c r="D89" t="n">
-        <v>0.007192729707836839</v>
+        <v>0.01002434286800214</v>
       </c>
       <c r="E89" t="n">
-        <v>0.8744098381334028</v>
+        <v>0.913275927802503</v>
       </c>
       <c r="F89" t="n">
-        <v>0.7896698580286738</v>
+        <v>0.8452757928901606</v>
       </c>
       <c r="G89" t="n">
-        <v>0.8985323651490581</v>
+        <v>0.9313931332491696</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>atis</t>
         </is>
       </c>
     </row>
@@ -3105,26 +3105,26 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.9260517935586083</v>
+        <v>0.953805209432068</v>
       </c>
       <c r="C90" t="n">
-        <v>0.8920880004795555</v>
+        <v>0.9273573217540559</v>
       </c>
       <c r="D90" t="n">
-        <v>0.0009719997376528575</v>
+        <v>0.001413396295181413</v>
       </c>
       <c r="E90" t="n">
-        <v>0.9040421605144178</v>
+        <v>0.9442371538995793</v>
       </c>
       <c r="F90" t="n">
-        <v>0.8419200850521342</v>
+        <v>0.9134751570893376</v>
       </c>
       <c r="G90" t="n">
-        <v>0.9252426176756972</v>
+        <v>0.960233545449913</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>atis</t>
         </is>
       </c>
     </row>
@@ -3135,26 +3135,26 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.6963421533928926</v>
+        <v>0.7553362763537471</v>
       </c>
       <c r="C91" t="n">
-        <v>0.6663861390100834</v>
+        <v>0.7173088631497999</v>
       </c>
       <c r="D91" t="n">
-        <v>3.054573883893243</v>
+        <v>4.825748408229051</v>
       </c>
       <c r="E91" t="n">
-        <v>0.380048477561065</v>
+        <v>0.4975964519837529</v>
       </c>
       <c r="F91" t="n">
-        <v>0.08803888595352771</v>
+        <v>0.1011437228168462</v>
       </c>
       <c r="G91" t="n">
-        <v>0.3850311947635027</v>
+        <v>0.4772118401106415</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>atis</t>
         </is>
       </c>
     </row>
